--- a/productos/06-contabilidad-basica/Contabilidad-Basica-para-Emprendedores.xlsx
+++ b/productos/06-contabilidad-basica/Contabilidad-Basica-para-Emprendedores.xlsx
@@ -123,7 +123,7 @@
     <t xml:space="preserve">7. Celdas protegidas</t>
   </si>
   <si>
-    <t xml:space="preserve">Las hojas están protegidas para que no borres fórmulas por accidente. Solo puedes escribir en las celdas resaltadas en color crema / texto azul. Contraseña de desprotección: plantilla2026.</t>
+    <t xml:space="preserve">Las hojas están protegidas para que no borres fórmulas por accidente. Solo puedes escribir en las celdas resaltadas en color crema / texto azul. Si necesitas editar otra celda, ve a Revisar → Desproteger hoja (no pide contraseña).</t>
   </si>
   <si>
     <t xml:space="preserve">Nota</t>
@@ -1420,11 +1420,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="57514162"/>
-        <c:axId val="38859629"/>
+        <c:axId val="62125264"/>
+        <c:axId val="32056575"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="57514162"/>
+        <c:axId val="62125264"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1456,7 +1456,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="38859629"/>
+        <c:crossAx val="32056575"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1464,7 +1464,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="38859629"/>
+        <c:axId val="32056575"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1506,7 +1506,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="57514162"/>
+        <c:crossAx val="62125264"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1778,11 +1778,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="32584369"/>
-        <c:axId val="65903961"/>
+        <c:axId val="37207572"/>
+        <c:axId val="83069746"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="32584369"/>
+        <c:axId val="37207572"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1814,7 +1814,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="65903961"/>
+        <c:crossAx val="83069746"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1822,7 +1822,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="65903961"/>
+        <c:axId val="83069746"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1864,7 +1864,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="32584369"/>
+        <c:crossAx val="37207572"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2366,7 +2366,7 @@
       <c r="F24" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="true" password="ee36" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
+  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
   <mergeCells count="16">
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="B4:F6"/>
@@ -2517,7 +2517,7 @@
       <c r="C28" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="true" password="ee36" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
+  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
   <mergeCells count="18">
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B4:C4"/>
@@ -2675,7 +2675,7 @@
       <c r="D14" s="20"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="true" password="ee36" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
+  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
   <mergeCells count="2">
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B14:D14"/>
@@ -2846,7 +2846,7 @@
       <c r="C16" s="20"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="true" password="ee36" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
+  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
   <mergeCells count="2">
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A16:C16"/>
@@ -5077,7 +5077,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection sheet="true" password="ee36" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
+  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A3:E3"/>
@@ -5824,7 +5824,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection sheet="true" password="ee36" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
+  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A3:N3"/>
@@ -5974,7 +5974,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection sheet="true" password="ee36" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
+  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
   <mergeCells count="10">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
